--- a/LoanOfficer-A/2023/76 huirem sunamani.xlsx
+++ b/LoanOfficer-A/2023/76 huirem sunamani.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10600</v>
+        <v>9400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -989,9 +989,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1015,9 +1021,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1041,9 +1053,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1067,9 +1085,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45606</v>
+      </c>
+      <c r="C20" s="4">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1093,9 +1117,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1119,9 +1149,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C22" s="4">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1145,9 +1181,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1171,9 +1213,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1197,9 +1245,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1223,9 +1277,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1249,9 +1309,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1275,9 +1341,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45611</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>

--- a/LoanOfficer-A/2023/76 huirem sunamani.xlsx
+++ b/LoanOfficer-A/2023/76 huirem sunamani.xlsx
@@ -437,7 +437,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,7 +489,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2600</v>
+        <v>4300</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9400</v>
+        <v>7700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -553,9 +553,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G3" s="4">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -585,9 +591,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G4" s="4">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -617,9 +629,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -649,9 +667,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -681,9 +705,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -713,9 +743,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -745,9 +781,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -777,9 +819,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -809,9 +857,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -841,9 +895,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -873,9 +933,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -905,9 +971,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -937,9 +1009,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1373,9 +1451,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1399,9 +1483,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C30" s="4">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1425,9 +1515,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C31" s="4">
+        <v>100</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1451,9 +1547,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C32" s="4">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>
